--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R3fe5054735534284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格" sheetId="1" r:id="R8ae9200c55514178"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -24,19 +24,8 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
-    <x:font>
-      <x:sz val="10"/>
-      <x:color rgb="FF243444"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="10"/>
-      <x:color rgb="FF243444"/>
-      <x:name val="Carlito"/>
-    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -45,101 +34,48 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF285D88"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFFF"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFEAF2F8"/>
+        <x:fgColor rgb="FF3C4F76"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="2">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFCFD8E3"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFCFD8E3"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFCFD8E3"/>
-      </x:top>
       <x:bottom style="thin">
-        <x:color rgb="FFCFD8E3"/>
-      </x:bottom>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFD9E2EC"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFD9E2EC"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFD9E2EC"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="FFD9E2EC"/>
+        <x:color rgb="FFD8DEE9"/>
       </x:bottom>
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TaskSpecTable" displayName="TaskSpecTable" ref="A1:B15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="2">
-    <x:tableColumn id="1" name="模块"/>
-    <x:tableColumn id="2" name="规格内容"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -338,136 +274,162 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="136" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="140" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="6" t="str">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="8" t="str">
         <x:v>模块</x:v>
       </x:c>
-      <x:c r="B1" s="6" t="str">
+      <x:c r="B1" s="8" t="str">
         <x:v>规格内容</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="31" customHeight="1">
-      <x:c r="A2" s="14" t="str">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="5" t="str">
         <x:v>任务ID</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
-        <x:v>ale-q2412</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="44" customHeight="1">
-      <x:c r="A3" s="14" t="str">
+      <x:c r="B2" s="5" t="str">
+        <x:v>callback_secret_rotation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="5" t="str">
         <x:v>主软件</x:v>
       </x:c>
-      <x:c r="B3" s="12" t="str">
-        <x:v>Helm3.18.4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="44" customHeight="1">
-      <x:c r="A4" s="14" t="str">
-        <x:v>业务目标</x:v>
-      </x:c>
-      <x:c r="B4" s="12" t="str">
-        <x:v>回调验签服务Chart的外部Secret轮换</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="44" customHeight="1">
-      <x:c r="A5" s="14" t="str">
+      <x:c r="B3" s="5" t="str">
+        <x:v>Helm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="5" t="str">
+        <x:v>辅助工具</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="str">
+        <x:v>PowerShell7、Python3.12、PyYAML6.0.2、UTF-8文本编辑器和CSV查看器</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="5" t="str">
         <x:v>输入来源</x:v>
       </x:c>
-      <x:c r="B5" s="12" t="str">
-        <x:v>题目输入数据包中的虚构或脱敏材料</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="57" customHeight="1">
-      <x:c r="A6" s="14" t="str">
-        <x:v>输入边界</x:v>
-      </x:c>
-      <x:c r="B6" s="12" t="str">
-        <x:v>输入目录只读，生成内容写入独立工作目录</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="70" customHeight="1">
-      <x:c r="A7" s="14" t="str">
+      <x:c r="B5" s="5" t="str">
+        <x:v>回调服务发布团队提供的Secret登记、轮换计划、发布合同、变更申请和当前Chart</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="5" t="str">
+        <x:v>输入获取方式</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="str">
+        <x:v>从输入数据包解压到本地只读目录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="5" t="str">
+        <x:v>原始输入文件</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="str">
+        <x:v>secret_registry.csv、phase_plan.csv、rotation_contract.json、change_request.md、README.md和starter目录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="5" t="str">
+        <x:v>目标输出文件</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="str">
+        <x:v>output/chart目录、output/rendered目录、output/reports/rotation_ledger.csv、output/reports/secret_reference_review.csv、output/change_note.md和output/README.md</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="5" t="str">
         <x:v>核心操作链</x:v>
       </x:c>
-      <x:c r="B7" s="12" t="str">
-        <x:v>从key_inventory.csv建立key_id到Secret名称的映射→按phase_plan.csv核对activeKey和acceptedKeys→使用projected volume引用每阶段所需Secret→在ConfigMap和Pod注解中写入阶段修订号→渲染四个有效阶段并检查两个失败关闭样例</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="70" customHeight="1">
-      <x:c r="A8" s="14" t="str">
-        <x:v>交付路径</x:v>
-      </x:c>
-      <x:c r="B8" s="12" t="str">
-        <x:v>output/charts/callback-keyring/Chart.yaml；output/charts/callback-keyring/templates/deployment.yaml；output/tools/audit_rotation.py；output/results/rotation_ledger.csv；output/results/negative_cases.csv；output/results/validation.json</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="57" customHeight="1">
-      <x:c r="A9" s="14" t="str">
-        <x:v>固定字段</x:v>
-      </x:c>
-      <x:c r="B9" s="12" t="str">
-        <x:v>rotation_contract.json的version为1.0；values.yaml的secretRefs.g17为callback-keyring-g17；values.yaml的secretRefs.g18为callback-keyring-g18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="44" customHeight="1">
-      <x:c r="A10" s="14" t="str">
-        <x:v>固定集合</x:v>
-      </x:c>
-      <x:c r="B10" s="12" t="str">
-        <x:v>轮换阶段包含steady；preload；activate；retire；Secret引用包含callback-keyring-g17；callback-keyring-g18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="57" customHeight="1">
-      <x:c r="A11" s="14" t="str">
-        <x:v>固定数值</x:v>
-      </x:c>
-      <x:c r="B11" s="12" t="str">
-        <x:v>有效阶段的数量为4个；错误场景的数量为2个</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="57" customHeight="1">
-      <x:c r="A12" s="14" t="str">
-        <x:v>允许变体</x:v>
-      </x:c>
-      <x:c r="B12" s="12" t="str">
-        <x:v>辅助模板可拆分</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="57" customHeight="1">
-      <x:c r="A13" s="14" t="str">
-        <x:v>Windows复现</x:v>
-      </x:c>
-      <x:c r="B13" s="12" t="str">
-        <x:v>主软件为Helm3.18.4，使用Windows11原生PowerShell运行helm.exe，无需WSL2。
-安装阶段可以联网取得主软件和锁定依赖，正式复现只读取题目输入并使用本机回环连接。辅助工具为PowerShell、Git和文本编辑器；公开仓库不包含凭据，许可按各软件原许可执行。
-建议准备2核CPU、4GB内存和2GB可用磁盘。权限限制为输入目录只读，程序只能写入指定工作目录；单次执行超时为15分钟，人工完成预计4至8小时。
-主要风险是把active切换和accepted集合收缩放在同一阶段，导致旧签名窗口提前关闭；</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="70" customHeight="1">
-      <x:c r="A14" s="14" t="str">
+      <x:c r="B9" s="5" t="str">
+        <x:v>核对Secret登记与阶段计划→调整Chart引用→同步运行配置→Helm渲染阶段清单→整理轮换台账→核对Secret引用→编写变更说明</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="5" t="str">
+        <x:v>轮换顺序</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="str">
+        <x:v>steady保留旧钥，preload加入新钥，activate启用新钥并保留旧钥，retire移除旧钥</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="5" t="str">
+        <x:v>Secret边界</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="str">
+        <x:v>Chart只引用平台托管Secret的名称和键名，不创建Secret对象，不处理密钥正文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="5" t="str">
+        <x:v>工作负载配置</x:v>
+      </x:c>
+      <x:c r="B12" s="5" t="str">
+        <x:v>Deployment投影顺序与acceptedKeys一致，ConfigMap、容器环境变量和Pod注解使用同一阶段值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="5" t="str">
+        <x:v>Chart校验</x:v>
+      </x:c>
+      <x:c r="B13" s="5" t="str">
+        <x:v>activeKey属于acceptedKeys，acceptedKeys中的代号都能在Secret登记表中找到</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="5" t="str">
+        <x:v>对象要求</x:v>
+      </x:c>
+      <x:c r="B14" s="5" t="str">
+        <x:v>合同指定的ConfigMap、Deployment和Service存在且身份唯一</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="5" t="str">
+        <x:v>报告设计</x:v>
+      </x:c>
+      <x:c r="B15" s="5" t="str">
+        <x:v>轮换台账按phase连接计划和清单，Secret引用核对表按phase与projection_order连接登记表和投影源</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="5" t="str">
+        <x:v>岗位衔接</x:v>
+      </x:c>
+      <x:c r="B16" s="5" t="str">
+        <x:v>发布评审人核对Chart、清单和报告，维护窗值班负责现场应用、验签观察和回滚</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="5" t="str">
         <x:v>完成条件</x:v>
       </x:c>
-      <x:c r="B14" s="12" t="str">
-        <x:v>总分100分。；；1.四阶段顺序、activeKey和acceptedKeys正确（25分）；2.Deployment投影的Secret名称和键路径正确（25分）；3.Chart不生成Secret对象且输入不含密钥正文（20分）；4.ConfigMap与Pod注解的阶段修订号一致（15分）；5.两个无效阶段在无清单输出时失败（15分）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="44" customHeight="1">
-      <x:c r="A15" s="14" t="str">
+      <x:c r="B17" s="5" t="str">
+        <x:v>Chart可由Helm检查并按计划生成清单，外部Secret边界、阶段配置、报告和变更说明互相一致</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="5" t="str">
+        <x:v>可验证点</x:v>
+      </x:c>
+      <x:c r="B18" s="5" t="str">
+        <x:v>交付路径、输入使用、轮换顺序、Secret引用、阶段配置、对象身份、失败关闭和跨产物一致性</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="6" t="str">
         <x:v>不适合作为评分点的内容</x:v>
       </x:c>
-      <x:c r="B15" s="12" t="str">
-        <x:v>文件缩进、换行、等价代码组织和本地绝对路径</x:v>
+      <x:c r="B19" s="6" t="str">
+        <x:v>YAML键序、注释、空白、文档顺序、CSV行序、Markdown章节名、代码函数名和临时目录</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re00292f164b44a48"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
--- a/task/任务规格转化.xlsx
+++ b/task/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格" sheetId="1" r:id="R8ae9200c55514178"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格" sheetId="1" r:id="Rcdc7dd13f3304c9d"/>
   </x:sheets>
 </x:workbook>
 </file>
